--- a/sources/标准汉语会话360句4_语法零基础版.xlsx
+++ b/sources/标准汉语会话360句4_语法零基础版.xlsx
@@ -4,9 +4,10 @@
   <workbookPr/>
   <sheets>
     <sheet name="01_语法总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_学生练习版" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_按课索引" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_说明与来源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="进阶练习" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_学生练习版" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_按课索引" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_说明与来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -15,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -26,8 +27,12 @@
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +57,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6A57A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B2A1F"/>
       </patternFill>
     </fill>
   </fills>
@@ -118,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -277,6 +287,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -2704,6 +2715,3296 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L65"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="62" t="inlineStr">
+        <is>
+          <t>语法编号</t>
+        </is>
+      </c>
+      <c r="B1" s="62" t="inlineStr">
+        <is>
+          <t>课次</t>
+        </is>
+      </c>
+      <c r="C1" s="62" t="inlineStr">
+        <is>
+          <t>题型</t>
+        </is>
+      </c>
+      <c r="D1" s="62" t="inlineStr">
+        <is>
+          <t>题干</t>
+        </is>
+      </c>
+      <c r="E1" s="62" t="inlineStr">
+        <is>
+          <t>选项A</t>
+        </is>
+      </c>
+      <c r="F1" s="62" t="inlineStr">
+        <is>
+          <t>选项B</t>
+        </is>
+      </c>
+      <c r="G1" s="62" t="inlineStr">
+        <is>
+          <t>选项C</t>
+        </is>
+      </c>
+      <c r="H1" s="62" t="inlineStr">
+        <is>
+          <t>选项D</t>
+        </is>
+      </c>
+      <c r="I1" s="62" t="inlineStr">
+        <is>
+          <t>答案</t>
+        </is>
+      </c>
+      <c r="J1" s="62" t="inlineStr">
+        <is>
+          <t>解析（中文）</t>
+        </is>
+      </c>
+      <c r="K1" s="62" t="inlineStr">
+        <is>
+          <t>解析（英文）</t>
+        </is>
+      </c>
+      <c r="L1" s="62" t="inlineStr">
+        <is>
+          <t>题干（英文）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>360-4.1.1</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>这个包你先拿___，别放在地上。</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>着</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>完</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>过</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>了</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>“拿着”表示一直拿在手里、保持这个状态，正好和“别放在地上”配合。“拿了”“拿完”是动作完成，不是持续。</t>
+        </is>
+      </c>
+      <c r="K2" s="14" t="inlineStr">
+        <is>
+          <t>拿着 means keep holding it — a continuing state, which matches 'don't put it on the floor'. 拿了/拿完 only show completion.</t>
+        </is>
+      </c>
+      <c r="L2" s="14" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>360-4.1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>我进去的时候，电视开着，___。</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>可是房间里没有人</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>所以我打开了电视</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>过了一会儿它才开</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>我就把电视打开了</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>“电视开着”说明电视当时已经处在开的状态，所以不能再说它后来才开或者我去打开它。</t>
+        </is>
+      </c>
+      <c r="K3" s="14" t="inlineStr">
+        <is>
+          <t>电视开着 says the TV was already on, so it can't come on later or need switching on.</t>
+        </is>
+      </c>
+      <c r="L3" s="14" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>360-4.1.1</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>外面下着了大雨。</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>窗户开着，屋里有点儿冷。</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>桌子上放着几本书。</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>她穿着一条红裙子。</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>“着”和“了”不能一起放在动词后面，应该说“外面下着大雨”。</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>着 and 了 cannot both follow the verb: 外面下着大雨.</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>360-4.1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>The door is closed, and nobody is at home.</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr"/>
+      <c r="F5" s="14" t="inlineStr"/>
+      <c r="G5" s="14" t="inlineStr"/>
+      <c r="H5" s="14" t="inlineStr"/>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>门关着，家里没有人。</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr"/>
+      <c r="K5" s="14" t="inlineStr"/>
+      <c r="L5" s="14" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>360-4.1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>她把房间擦得___的。</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>干净干净</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>干净净</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>很干干净净</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>干干净净</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>双音节形容词AB重叠成AABB：干干净净。重叠以后已经有程度意思，前面不能再加“很”。</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>A two-syllable adjective AB repeats as AABB: 干干净净. It already sounds strong, so no 很 before it.</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>360-4.1.2</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>这碗面条儿___的，快吃吧。</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>很热热</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>热了热</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>不热热</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>热热</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>形容词重叠后已经有程度的意思，前面不能加“很、不”，中间也不能加“了”：热热的。</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
+        <is>
+          <t>A reduplicated adjective already shows degree, so no 很/不 before it and no 了 inside: 热热的.</t>
+        </is>
+      </c>
+      <c r="L7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>360-4.1.2</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>这个苹果红红的，真好看。</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>外面黑黑的，什么也看不见。</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>她的头发很长长的。</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>他个子高高的。</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>重叠的形容词前面不能用“很”，应该说“她的头发长长的”。</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>Do not use 很 before a reduplicated adjective: 她的头发长长的.</t>
+        </is>
+      </c>
+      <c r="L8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>360-4.1.2</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Grandpa slowly walked into the park.</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>爷爷慢慢地走进了公园。</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr"/>
+      <c r="K9" s="14" t="inlineStr"/>
+      <c r="L9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>360-4.2.1</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>我___你的衣服洗干净了。</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>让</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>被</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>把</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>“我”是做动作的人，“你的衣服”是被处理的东西，要用“把”。“被”会让意思变成衣服对我做了什么。</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>我 does the action and 你的衣服 is what is handled, so use 把. 被 would make the clothes the doer.</t>
+        </is>
+      </c>
+      <c r="L10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>360-4.2.1</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>请把垃圾___。</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>扔</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>扔着</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>扔过</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>扔掉</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>“把”字句的动词后面要有结果等其他成分：扔掉。光杆动词“扔”不行，“着、过”也不能这样用。</t>
+        </is>
+      </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>In a 把 sentence the verb needs a result after it: 扔掉. A bare 扔 won't do, and 着/过 don't work here.</t>
+        </is>
+      </c>
+      <c r="L11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>360-4.2.1</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>他把手机丢了。</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>你把这些书放在书柜里吧。</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>请把电视关上。</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>我把票没带来。</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>否定词要放在“把”前面，应该说“我没把票带来”。</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>The negative goes before 把: 我没把票带来.</t>
+        </is>
+      </c>
+      <c r="L12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>360-4.2.1</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>I've cleaned the window.（用“把”）</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>我把窗户擦干净了。</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr"/>
+      <c r="K13" s="14" t="inlineStr"/>
+      <c r="L13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>360-4.2.2</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>我太累了，___饭都不想吃了。</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>才</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>连</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>还</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>就</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t>“……都……”前面说出一个极端的例子，要用“连”：连饭都不想吃。</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>To name an extreme example before 都, use 连: 连饭都不想吃.</t>
+        </is>
+      </c>
+      <c r="L14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>360-4.2.2</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>这个问题太容易了，连___都会回答。</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>小孩子</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>老师</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>大学生</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>大人</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>“连”后面要放最让人意外的例子。问题很容易，连小孩子都会，才说明容易；老师、大人会是很正常的。</t>
+        </is>
+      </c>
+      <c r="K15" s="14" t="inlineStr">
+        <is>
+          <t>连 introduces the most surprising example. For an easy question that's a small child; a teacher or adult knowing it is no surprise.</t>
+        </is>
+      </c>
+      <c r="L15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>360-4.2.2</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>他连一句汉语也不会说。</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>我连一分钱都没有了。</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>这个菜太辣了，连哥哥不吃。</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>这件事连他妈妈都不知道。</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J16" s="14" t="inlineStr">
+        <is>
+          <t>“连”后面要有“都”或“也”配合：连哥哥都不吃。</t>
+        </is>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>连 must be followed by 都 or 也: 连哥哥都不吃.</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>360-4.2.2</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>He is so busy that he doesn't even have time to sleep.</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr">
+        <is>
+          <t>他忙得连睡觉的时间都没有。</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>360-4.3.1</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>他___听音乐，一边做作业。</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>一起</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>一直</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>一边</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>一下</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J18" s="14" t="inlineStr">
+        <is>
+          <t>后面有“一边做作业”，前面也要用“一边”，表示两个动作同时进行。</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>Since 一边做作业 follows, the first part also needs 一边 — two actions at once.</t>
+        </is>
+      </c>
+      <c r="L18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>360-4.3.1</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>我们一边喝茶，一边___。</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>聊完了天儿</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>到了机场</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>很开心</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>聊天儿</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>“一边”后面要放可以同时进行的动作，不能放形容词，也不能放已经完成的动作。</t>
+        </is>
+      </c>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>一边 needs an action that goes on at the same time — not an adjective or a finished action.</t>
+        </is>
+      </c>
+      <c r="L19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>360-4.3.1</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>爸爸一边吃早饭，一边看报纸。</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>他一边高兴，一边唱歌。</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>他一边看说明书，一边安装书柜。</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>他一边洗衣服，一边唱歌。</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
+        <is>
+          <t>“一边”后面要用动作，不能用形容词，可以说“他一边唱歌，一边笑”或“他高高兴兴地唱歌”。</t>
+        </is>
+      </c>
+      <c r="K20" s="14" t="inlineStr">
+        <is>
+          <t>一边 needs an action, not an adjective: 他高高兴兴地唱歌.</t>
+        </is>
+      </c>
+      <c r="L20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>360-4.3.1</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>Don't look at your phone while walking.</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr"/>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>别一边走路一边看手机。</t>
+        </is>
+      </c>
+      <c r="J21" s="14" t="inlineStr"/>
+      <c r="K21" s="14" t="inlineStr"/>
+      <c r="L21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>360-4.3.2</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>我们___吧，别站着了。</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>坐过聊</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>坐在聊</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>坐着聊</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>坐了聊</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>“动词1＋着＋动词2”表示用什么样子做第二个动作：坐着聊。“了、过”不能这样用。</t>
+        </is>
+      </c>
+      <c r="K22" s="14" t="inlineStr">
+        <is>
+          <t>Verb1 + 着 + Verb2 shows the manner of the second action: 坐着聊. 了 and 过 can't be used this way.</t>
+        </is>
+      </c>
+      <c r="L22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>360-4.3.2</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>那个孩子笑着___。</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>笑了一下</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>笑起来了</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>开心了</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>跑过来了</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>“笑着”说明做第二个动作的样子，后面要接另一个动作，不能再接“笑”或形容词。</t>
+        </is>
+      </c>
+      <c r="K23" s="14" t="inlineStr">
+        <is>
+          <t>笑着 describes how the next action is done, so it must be followed by a different action, not 笑 again or an adjective.</t>
+        </is>
+      </c>
+      <c r="L23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>360-4.3.2</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>孩子坐吃着饭。</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>她唱着歌走进了教室。</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>他拿着杯子喝茶。</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>我们走着去吧。</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>“着”要放在第一个动词后面：孩子坐着吃饭。</t>
+        </is>
+      </c>
+      <c r="K24" s="14" t="inlineStr">
+        <is>
+          <t>着 goes after the first verb: 孩子坐着吃饭.</t>
+        </is>
+      </c>
+      <c r="L24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>360-4.3.2</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Don't eat standing up — sit down and eat.</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr"/>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr">
+        <is>
+          <t>别站着吃，坐下吃吧。</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr"/>
+      <c r="K25" s="14" t="inlineStr"/>
+      <c r="L25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>360-4.4.1</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>我的自行车___朋友借走了。</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>把</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>被</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>跟</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J26" s="14" t="inlineStr">
+        <is>
+          <t>自行车是接受动作的，朋友是做动作的人，要用“被”。用“把”就变成自行车去借朋友了。</t>
+        </is>
+      </c>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>The bike receives the action and the friend does it, so use 被. With 把 the bike would be the one borrowing.</t>
+        </is>
+      </c>
+      <c r="L26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>360-4.4.1</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>我的手机被人___。</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>弄着</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>弄坏了</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>弄</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>坏了</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>“被”字句的动词后面一般要有结果，而且要有动作动词：弄坏了。“坏了”没有动作，不能直接放在“被人”后面。</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>A 被 sentence needs an action verb plus a result: 弄坏了. 坏了 has no action verb, and a bare 弄 has no result.</t>
+        </is>
+      </c>
+      <c r="L27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>360-4.4.1</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>我的车叫朋友开走了。</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>那棵树被车撞倒了。</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>我的蛋糕被弟弟没吃完。</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>我的书让同学借走了。</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>否定词放在“被”前面：我的蛋糕没被弟弟吃完。</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>The negative goes before 被: 我的蛋糕没被弟弟吃完.</t>
+        </is>
+      </c>
+      <c r="L28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>360-4.4.1</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>My bike was hit by a car and broken.</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr"/>
+      <c r="F29" s="14" t="inlineStr"/>
+      <c r="G29" s="14" t="inlineStr"/>
+      <c r="H29" s="14" t="inlineStr"/>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>我的自行车被车撞坏了。</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr"/>
+      <c r="K29" s="14" t="inlineStr"/>
+      <c r="L29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>360-4.4.2</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>你天天上网，___连这个都不知道吗？</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>为什么</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>怎么样</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>难道</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>到底</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>“难道……吗？”是反问，意思是“你应该知道”。“到底、为什么”是真的问问题，不能和“吗”一起用。</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>难道…吗? is rhetorical: 'surely you know'. 到底 and 为什么 ask real questions and can't go with 吗.</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>360-4.4.2</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>你不是会说汉语吗？___。</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>你跟他说吧</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>我不知道你会说</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>我知道你不会说</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>你应该先学汉语</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>“不是……吗？”表示说话人认为你会说汉语，所以后面自然是请你去说。</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>不是…吗? means the speaker believes you DO speak Chinese, so the natural follow-up is asking you to talk to him.</t>
+        </is>
+      </c>
+      <c r="L31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>360-4.4.2</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>难道你忘了今天是我的生日吧？</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>他不是已经出院了吗？</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>你怎么能把我的书扔了呢？</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>这不是你昨天买的衣服吗？</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
+        <is>
+          <t>“难道”要和“吗”配合，不用“吧”：难道你忘了今天是我的生日吗？</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>难道 pairs with 吗, not 吧: 难道你忘了今天是我的生日吗？</t>
+        </is>
+      </c>
+      <c r="L32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>360-4.4.2</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>Didn't you say you would come?</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr"/>
+      <c r="G33" s="14" t="inlineStr"/>
+      <c r="H33" s="14" t="inlineStr"/>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>你不是说你会来吗？</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr"/>
+      <c r="K33" s="14" t="inlineStr"/>
+      <c r="L33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>360-4.5.1</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>这家宾馆不但便宜，___离地铁站很近。</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>而且</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>可是</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>所以</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>而是</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>“不但”后面要用“而且”再加上一个优点。“而是”用在“不是……而是……”里，“可是”表示转折。</t>
+        </is>
+      </c>
+      <c r="K34" s="14" t="inlineStr">
+        <is>
+          <t>不但 is followed by 而且 to add another point. 而是 belongs to 不是…而是…, and 可是 shows contrast.</t>
+        </is>
+      </c>
+      <c r="L34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>360-4.5.1</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>这件衣服不但不好看，而且___。</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>很舒服</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>很贵</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>很便宜</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>很合适</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>“不但……而且……”后一部分要和前一部分方向一样，再进一步。前面说缺点，后面也应该是缺点。</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr">
+        <is>
+          <t>The second part of 不但…而且… goes the same way as the first. A drawback must be followed by another drawback.</t>
+        </is>
+      </c>
+      <c r="L35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>360-4.5.1</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>不但她喜欢做饭，而且做得很好。</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>不但我喜欢，而且我妈妈也喜欢。</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>他不但是我的老师，而且是我的朋友。</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>这里不但离学校近，而且很便宜。</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
+        <is>
+          <t>前后主语相同时，主语要放在“不但”前面：她不但喜欢做饭，而且做得很好。</t>
+        </is>
+      </c>
+      <c r="K36" s="14" t="inlineStr">
+        <is>
+          <t>When both parts have the same subject, put it before 不但: 她不但喜欢做饭，而且做得很好.</t>
+        </is>
+      </c>
+      <c r="L36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>360-4.5.1</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>My friend not only came, but also brought a cake.</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr"/>
+      <c r="F37" s="14" t="inlineStr"/>
+      <c r="G37" s="14" t="inlineStr"/>
+      <c r="H37" s="14" t="inlineStr"/>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>我朋友不但来了，而且带来了一个蛋糕。</t>
+        </is>
+      </c>
+      <c r="J37" s="14" t="inlineStr"/>
+      <c r="K37" s="14" t="inlineStr"/>
+      <c r="L37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>360-4.5.2</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>___路上堵车，所以我来晚了。</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>虽然</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>为了</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>要是</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>后面有“所以”，前面说原因，要用“因为”。“为了”说目的，不说原因。</t>
+        </is>
+      </c>
+      <c r="K38" s="14" t="inlineStr">
+        <is>
+          <t>所以 follows a reason, so use 因为. 为了 gives a purpose, not a cause.</t>
+        </is>
+      </c>
+      <c r="L38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>360-4.5.2</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>因为最近天气很冷，所以___。</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>我穿得很少</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>我不想穿厚衣服</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>我感冒了</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>我觉得很热</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>“所以”后面是前面原因带来的结果。天冷的结果是感冒了，不是觉得热或少穿衣服。</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>The part after 所以 must be a result of the reason. Cold weather leads to a cold, not to feeling hot or wearing less.</t>
+        </is>
+      </c>
+      <c r="L39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>360-4.5.2</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>因为他很认真，所以成绩很好。</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>因为下雨了，他所以没来。</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>我没去，因为我发烧了。</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>因为堵车，所以我们来晚了。</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>“所以”要放在后一分句的开头，主语前面：因为下雨了，所以他没来。</t>
+        </is>
+      </c>
+      <c r="K40" s="14" t="inlineStr">
+        <is>
+          <t>所以 goes at the start of the second clause, before the subject: 所以他没来.</t>
+        </is>
+      </c>
+      <c r="L40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>360-4.5.2</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>Because the hotel was full, we went to another one.</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+      <c r="F41" s="14" t="inlineStr"/>
+      <c r="G41" s="14" t="inlineStr"/>
+      <c r="H41" s="14" t="inlineStr"/>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>因为宾馆满了，所以我们去了别的宾馆。</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr"/>
+      <c r="K41" s="14" t="inlineStr"/>
+      <c r="L41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>360-4.6.1</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>___你明天有空，我们就去博物馆吧。</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>如果</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>只有</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>不但</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>虽然</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J42" s="14" t="inlineStr">
+        <is>
+          <t>前面是条件，后面用“就”，要用“如果”。“只有”要和“才”配合。</t>
+        </is>
+      </c>
+      <c r="K42" s="14" t="inlineStr">
+        <is>
+          <t>A condition followed by 就 takes 如果. 只有 must pair with 才.</t>
+        </is>
+      </c>
+      <c r="L42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>360-4.6.1</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>如果你找不到路，___。</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>所以给我打电话</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>就给我打电话</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>就给我打了电话</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>才给我打电话</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>“如果……就……”说还没发生的事，“就”后面不用“了”；“才、所以”不和“如果”配合。</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="inlineStr">
+        <is>
+          <t>如果…就… is about what hasn't happened, so no 了 after 就; 才 and 所以 don't pair with 如果.</t>
+        </is>
+      </c>
+      <c r="L43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>360-4.6.1</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>如果有问题，就问我。</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>如果你喜欢，我就送给你。</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>如果明天不下雨，我们就去郊区玩儿。</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>如果你想家，才给妈妈打电话吧。</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>“如果”要和“就”配合：如果你想家，就给妈妈打电话吧。</t>
+        </is>
+      </c>
+      <c r="K44" s="14" t="inlineStr">
+        <is>
+          <t>如果 pairs with 就: 如果你想家，就给妈妈打电话吧.</t>
+        </is>
+      </c>
+      <c r="L44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>360-4.6.1</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>If you're busy, I'll go by myself.</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr"/>
+      <c r="F45" s="14" t="inlineStr"/>
+      <c r="G45" s="14" t="inlineStr"/>
+      <c r="H45" s="14" t="inlineStr"/>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>如果你忙，我就自己去。</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr"/>
+      <c r="K45" s="14" t="inlineStr"/>
+      <c r="L45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>360-4.6.2</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>___学好汉语，他每天都看中国电影。</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>如果</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>为了</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>所以</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J46" s="14" t="inlineStr">
+        <is>
+          <t>“学好汉语”是他想达到的目的，所以用“为了”。“因为”说已经有的原因。</t>
+        </is>
+      </c>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>学好汉语 is the goal he wants to reach, so use 为了. 因为 gives an existing cause.</t>
+        </is>
+      </c>
+      <c r="L46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>360-4.6.2</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>为了___，他每天晚上十点就睡觉。</t>
+        </is>
+      </c>
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>身体不好</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>睡得很晚</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>早点儿起床</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>天气太冷</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>“为了”后面要放目的，就是想做到的事。“身体不好、天气太冷”是原因或情况，不是目的。</t>
+        </is>
+      </c>
+      <c r="K47" s="14" t="inlineStr">
+        <is>
+          <t>为了 must be followed by a goal. 身体不好 and 天气太冷 are causes or situations, not goals.</t>
+        </is>
+      </c>
+      <c r="L47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>360-4.6.2</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>为了参加比赛，她每天锻炼。</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>他为了照顾妈妈，回国了。</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>为了节省时间，我们坐高铁去。</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>为了下雨，我们没去郊区。</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>下雨是原因，不是目的，应该说“因为下雨，我们没去郊区”。</t>
+        </is>
+      </c>
+      <c r="K48" s="14" t="inlineStr">
+        <is>
+          <t>Rain is a cause, not a goal: 因为下雨，我们没去郊区.</t>
+        </is>
+      </c>
+      <c r="L48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>360-4.6.2</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>She cooks at home every day in order to save money.</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr"/>
+      <c r="F49" s="14" t="inlineStr"/>
+      <c r="G49" s="14" t="inlineStr"/>
+      <c r="H49" s="14" t="inlineStr"/>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>为了省钱，她每天在家做饭。</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr"/>
+      <c r="K49" s="14" t="inlineStr"/>
+      <c r="L49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>360-4.7.1</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>菜单上的字太小了，我看___清楚。</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>没</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>不</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>得</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>字太小，所以看不清楚，用“不”构成可能补语的否定。“没”说的是结果，不放在动词和补语中间。</t>
+        </is>
+      </c>
+      <c r="K50" s="14" t="inlineStr">
+        <is>
+          <t>The print is too small, so it can't be read: use 不 between verb and result. 没 never goes between them.</t>
+        </is>
+      </c>
+      <c r="L50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>360-4.7.1</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>这么多菜，我们两个人肯定___。</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>吃得不完</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>不吃得完</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>吃完不了</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>吃不完</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>说因为数量太多做不到，要用可能补语“吃不完”，“不”放在动词和补语中间。</t>
+        </is>
+      </c>
+      <c r="K51" s="14" t="inlineStr">
+        <is>
+          <t>To say it's impossible, use the potential form 吃不完, with 不 between the verb and the result.</t>
+        </is>
+      </c>
+      <c r="L51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>360-4.7.1</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>老师说得太快，我听得不懂。</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>坐在后面也看得清楚。</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>这么多作业，今天做得完吗？</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>门太小了，床搬不进去。</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J52" s="14" t="inlineStr">
+        <is>
+          <t>可能补语的否定是“动词＋不＋补语”：我听不懂。</t>
+        </is>
+      </c>
+      <c r="K52" s="14" t="inlineStr">
+        <is>
+          <t>The negative potential form is verb + 不 + result: 我听不懂.</t>
+        </is>
+      </c>
+      <c r="L52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>360-4.7.1</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>I can't find my phone.</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr"/>
+      <c r="F53" s="14" t="inlineStr"/>
+      <c r="G53" s="14" t="inlineStr"/>
+      <c r="H53" s="14" t="inlineStr"/>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>我找不到我的手机了。</t>
+        </is>
+      </c>
+      <c r="J53" s="14" t="inlineStr"/>
+      <c r="K53" s="14" t="inlineStr"/>
+      <c r="L53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>360-4.7.2</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>他从楼上走___来，在门口等我。</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>进</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>出</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J54" s="14" t="inlineStr">
+        <is>
+          <t>从楼上到楼下，方向是向下，所以说“走下来”。</t>
+        </is>
+      </c>
+      <c r="K54" s="14" t="inlineStr">
+        <is>
+          <t>Coming from upstairs means moving down, so it's 走下来.</t>
+        </is>
+      </c>
+      <c r="L54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>360-4.7.2</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>他从外面跑进来，___。</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>坐在我旁边</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>站在门外面</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>一直在外面玩儿</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>在马路上等我</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>“跑进来”说明他进到了说话人所在的里面，所以应该在“我”旁边，不在外面。</t>
+        </is>
+      </c>
+      <c r="K55" s="14" t="inlineStr">
+        <is>
+          <t>跑进来 means he came inside to where the speaker is, so he ends up next to me, not outside.</t>
+        </is>
+      </c>
+      <c r="L55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>360-4.7.2</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>妈妈从外面走进来了。</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>他走进去教室了。</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>他从包里拿出一本书来。</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>请把垃圾拿出去。</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J56" s="14" t="inlineStr">
+        <is>
+          <t>表示地方的宾语要放在“来/去”前面：他走进教室去了。</t>
+        </is>
+      </c>
+      <c r="K56" s="14" t="inlineStr">
+        <is>
+          <t>A place object goes before 来/去: 他走进教室去了.</t>
+        </is>
+      </c>
+      <c r="L56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>360-4.7.2</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>He ran back to the dorm.</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr"/>
+      <c r="F57" s="14" t="inlineStr"/>
+      <c r="G57" s="14" t="inlineStr"/>
+      <c r="H57" s="14" t="inlineStr"/>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>他跑回宿舍去了。</t>
+        </is>
+      </c>
+      <c r="J57" s="14" t="inlineStr"/>
+      <c r="K57" s="14" t="inlineStr"/>
+      <c r="L57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>360-4.8.1</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>___买了票，才能进去看比赛。</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>因为</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>只有</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>只要</t>
+        </is>
+      </c>
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>如果</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J58" s="14" t="inlineStr">
+        <is>
+          <t>后面用“才能”，前面说唯一的条件，要用“只有”。“只要”要和“就”配合。</t>
+        </is>
+      </c>
+      <c r="K58" s="14" t="inlineStr">
+        <is>
+          <t>才能 needs 只有 for the one necessary condition. 只要 pairs with 就.</t>
+        </is>
+      </c>
+      <c r="L58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>360-4.8.1</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>只有你自己去，___。</t>
+        </is>
+      </c>
+      <c r="E59" s="14" t="inlineStr">
+        <is>
+          <t>都能拿到快递</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>就能拿到快递</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>才能拿到快递</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>也能拿到快递</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J59" s="14" t="inlineStr">
+        <is>
+          <t>“只有”说唯一的条件，后面要用“才（能）”配合。</t>
+        </is>
+      </c>
+      <c r="K59" s="14" t="inlineStr">
+        <is>
+          <t>只有 states the only condition and must be followed by 才(能).</t>
+        </is>
+      </c>
+      <c r="L59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>360-4.8.1</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>只有大夫说可以，你才能出院。</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>只有天气好，我们就去爬山。</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>只有八点以前出门，才能坐上车。</t>
+        </is>
+      </c>
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>只有多锻炼，身体才会好。</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J60" s="14" t="inlineStr">
+        <is>
+          <t>“只有”要和“才”配合：只有天气好，我们才去爬山。</t>
+        </is>
+      </c>
+      <c r="K60" s="14" t="inlineStr">
+        <is>
+          <t>只有 pairs with 才: 只有天气好，我们才去爬山.</t>
+        </is>
+      </c>
+      <c r="L60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>360-4.8.1</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>Only if you rest well will you get better.</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr"/>
+      <c r="F61" s="14" t="inlineStr"/>
+      <c r="G61" s="14" t="inlineStr"/>
+      <c r="H61" s="14" t="inlineStr"/>
+      <c r="I61" s="14" t="inlineStr">
+        <is>
+          <t>只有好好休息，你的病才能好。</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr"/>
+      <c r="K61" s="14" t="inlineStr"/>
+      <c r="L61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>360-4.8.2</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>辨析</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>我___看见他就想笑。</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>才</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>都</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>先</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J62" s="14" t="inlineStr">
+        <is>
+          <t>“一……就……”表示前一个动作发生，后一个马上跟着发生：一看见他就想笑。</t>
+        </is>
+      </c>
+      <c r="K62" s="14" t="inlineStr">
+        <is>
+          <t>一…就… means the second thing follows right after the first: 一看见他就想笑.</t>
+        </is>
+      </c>
+      <c r="L62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>360-4.8.2</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>他一到家，___。</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>才打开了电视</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>还打开了电视</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>再打开电视</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>就打开了电视</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="inlineStr">
+        <is>
+          <t>“一……就……”表示前一个动作发生后马上做后一个，所以要用“就”。</t>
+        </is>
+      </c>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>一…就… means the second action follows right after the first, so use 就.</t>
+        </is>
+      </c>
+      <c r="L63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>360-4.8.2</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>找错</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>下面哪一句有错？</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>他一有问题就问老师。</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>天气一冷，我就感冒。</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>我一看见这张照片就想家。</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>我一吃完饭，回宿舍了。</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="inlineStr">
+        <is>
+          <t>“一”后面要有“就”配合：我一吃完饭就回宿舍了。</t>
+        </is>
+      </c>
+      <c r="K64" s="14" t="inlineStr">
+        <is>
+          <t>一 needs 就: 我一吃完饭就回宿舍了.</t>
+        </is>
+      </c>
+      <c r="L64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>360-4.8.2</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>翻译</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>As soon as he got on the train, he fell asleep.</t>
+        </is>
+      </c>
+      <c r="E65" s="14" t="inlineStr"/>
+      <c r="F65" s="14" t="inlineStr"/>
+      <c r="G65" s="14" t="inlineStr"/>
+      <c r="H65" s="14" t="inlineStr"/>
+      <c r="I65" s="14" t="inlineStr">
+        <is>
+          <t>他一上火车就睡着了。</t>
+        </is>
+      </c>
+      <c r="J65" s="14" t="inlineStr"/>
+      <c r="K65" s="14" t="inlineStr"/>
+      <c r="L65" s="14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4181,7 +7482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4416,13 +7717,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -4561,6 +7862,18 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>进阶练习（网站，2026-10）</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>「进阶练习」表是为网站新写的进阶题：每个语法点辨析选择、完成句子、找错各 1 道（点选作答，带中英文解析；入门册另附题干英文），难度按本册水平控制，经出题、正确性+难度审核、终审三轮把关。网站上它们替换了 01 表「练习1–3」中的填空/选择/排序等题；翻译题保留，其中答案与例句完全相同的，在本表换成了新句子（题型=翻译）。01 表原有练习未改动。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
